--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_30-10-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_30-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Ecotherm_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179D1290-8E81-416F-A470-9B2349757959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7631BDA-E58A-4967-A3BB-BD6880E7AA52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32025" yWindow="1545" windowWidth="21600" windowHeight="10230" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31680" yWindow="180" windowWidth="21600" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -484,45 +484,6 @@
     <t>£54.99</t>
   </si>
   <si>
-    <t>£13.66</t>
-  </si>
-  <si>
-    <t>£16.36</t>
-  </si>
-  <si>
-    <t>£23.95</t>
-  </si>
-  <si>
-    <t>£21.08</t>
-  </si>
-  <si>
-    <t>£25.78</t>
-  </si>
-  <si>
-    <t>£29.39</t>
-  </si>
-  <si>
-    <t>£34.72</t>
-  </si>
-  <si>
-    <t>£39.97</t>
-  </si>
-  <si>
-    <t>£35.78</t>
-  </si>
-  <si>
-    <t>£34.70</t>
-  </si>
-  <si>
-    <t>£51.98</t>
-  </si>
-  <si>
-    <t>£53.56</t>
-  </si>
-  <si>
-    <t>£51.95</t>
-  </si>
-  <si>
     <t>£13.90</t>
   </si>
   <si>
@@ -590,6 +551,45 @@
   </si>
   <si>
     <t>£76.96</t>
+  </si>
+  <si>
+    <t>£13.59</t>
+  </si>
+  <si>
+    <t>£16.28</t>
+  </si>
+  <si>
+    <t>£23.83</t>
+  </si>
+  <si>
+    <t>£20.97</t>
+  </si>
+  <si>
+    <t>£25.65</t>
+  </si>
+  <si>
+    <t>£29.24</t>
+  </si>
+  <si>
+    <t>£34.55</t>
+  </si>
+  <si>
+    <t>£39.77</t>
+  </si>
+  <si>
+    <t>£35.60</t>
+  </si>
+  <si>
+    <t>£34.53</t>
+  </si>
+  <si>
+    <t>£51.72</t>
+  </si>
+  <si>
+    <t>£53.29</t>
+  </si>
+  <si>
+    <t>£51.69</t>
   </si>
 </sst>
 </file>
@@ -1022,13 +1022,13 @@
         <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="G2" t="s">
         <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="I2" t="s">
         <v>139</v>
@@ -1046,7 +1046,7 @@
         <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="O2" t="s">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="G3" t="s">
         <v>29</v>
       </c>
       <c r="H3" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="I3" t="s">
         <v>140</v>
@@ -1096,7 +1096,7 @@
         <v>32</v>
       </c>
       <c r="N3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="O3" t="s">
         <v>24</v>
@@ -1122,13 +1122,13 @@
         <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="G4" t="s">
         <v>37</v>
       </c>
       <c r="H4" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="I4" t="s">
         <v>141</v>
@@ -1146,7 +1146,7 @@
         <v>40</v>
       </c>
       <c r="N4" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="O4" t="s">
         <v>24</v>
@@ -1172,13 +1172,13 @@
         <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="G5" t="s">
         <v>45</v>
       </c>
       <c r="H5" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I5" t="s">
         <v>142</v>
@@ -1196,7 +1196,7 @@
         <v>48</v>
       </c>
       <c r="N5" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="O5" t="s">
         <v>24</v>
@@ -1222,13 +1222,13 @@
         <v>52</v>
       </c>
       <c r="F6" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="G6" t="s">
         <v>53</v>
       </c>
       <c r="H6" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="I6" t="s">
         <v>143</v>
@@ -1246,7 +1246,7 @@
         <v>56</v>
       </c>
       <c r="N6" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="O6" t="s">
         <v>24</v>
@@ -1272,13 +1272,13 @@
         <v>60</v>
       </c>
       <c r="F7" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="G7" t="s">
         <v>61</v>
       </c>
       <c r="H7" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="I7" t="s">
         <v>144</v>
@@ -1296,7 +1296,7 @@
         <v>64</v>
       </c>
       <c r="N7" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="O7" t="s">
         <v>24</v>
@@ -1322,7 +1322,7 @@
         <v>68</v>
       </c>
       <c r="F8" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="G8" t="s">
         <v>69</v>
@@ -1346,7 +1346,7 @@
         <v>73</v>
       </c>
       <c r="N8" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="O8" t="s">
         <v>24</v>
@@ -1372,7 +1372,7 @@
         <v>77</v>
       </c>
       <c r="F9" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="G9" t="s">
         <v>78</v>
@@ -1396,7 +1396,7 @@
         <v>82</v>
       </c>
       <c r="N9" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="O9" t="s">
         <v>24</v>
@@ -1422,7 +1422,7 @@
         <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="G10" t="s">
         <v>87</v>
@@ -1472,13 +1472,13 @@
         <v>95</v>
       </c>
       <c r="F11" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="G11" t="s">
         <v>96</v>
       </c>
       <c r="H11" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="I11" t="s">
         <v>147</v>
@@ -1528,7 +1528,7 @@
         <v>103</v>
       </c>
       <c r="H12" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="I12" t="s">
         <v>148</v>
@@ -1546,7 +1546,7 @@
         <v>105</v>
       </c>
       <c r="N12" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="O12" t="s">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         <v>109</v>
       </c>
       <c r="F13" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="G13" t="s">
         <v>110</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="I13" t="s">
         <v>148</v>
@@ -1596,7 +1596,7 @@
         <v>113</v>
       </c>
       <c r="N13" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="O13" t="s">
         <v>24</v>
@@ -1628,7 +1628,7 @@
         <v>118</v>
       </c>
       <c r="H14" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="I14" t="s">
         <v>149</v>
@@ -1646,7 +1646,7 @@
         <v>121</v>
       </c>
       <c r="N14" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s">
         <v>24</v>
@@ -1672,7 +1672,7 @@
         <v>125</v>
       </c>
       <c r="F15" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="G15" t="s">
         <v>126</v>
@@ -1722,13 +1722,13 @@
         <v>133</v>
       </c>
       <c r="F16" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="G16" t="s">
         <v>134</v>
       </c>
       <c r="H16" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="I16" t="s">
         <v>151</v>
@@ -1746,7 +1746,7 @@
         <v>137</v>
       </c>
       <c r="N16" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="O16" t="s">
         <v>24</v>
